--- a/Team_Files/Bill of Materials.xlsx
+++ b/Team_Files/Bill of Materials.xlsx
@@ -902,12 +902,12 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>MATE / DISL</t>
+          <t>MATE</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>2027 Northern Gulf Coast Regional</t>
+          <t>2027 regional (assignment TBD)</t>
         </is>
       </c>
       <c r="E7" s="16" t="n">
@@ -942,7 +942,7 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>Dauphin Island, AL — 6 hr drive</t>
+          <t>Travel to our 2027 regional (TBD)</t>
         </is>
       </c>
       <c r="E8" s="16" t="n">

--- a/Team_Files/Bill of Materials.xlsx
+++ b/Team_Files/Bill of Materials.xlsx
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>2800</v>
+        <v>2880</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>1050</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>2320</v>
+        <v>2410</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>300</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1400</v>
+        <v>1580</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>0</v>
@@ -902,12 +902,12 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>MATE</t>
+          <t>MATE / DISL</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>2027 regional (assignment TBD)</t>
+          <t>2027 Northern Gulf Coast Regional</t>
         </is>
       </c>
       <c r="E7" s="16" t="n">
@@ -942,7 +942,7 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>Travel to our 2027 regional (TBD)</t>
+          <t>Dauphin Island, AL — 6 hr drive</t>
         </is>
       </c>
       <c r="E8" s="16" t="n">
@@ -991,7 +991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1217,21 +1217,56 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="n"/>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="A11" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>12 V SLA battery + charger + approved enclosure (Phase 1 power, 1.5–1.7 gate)</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Amazon / Powerwerx</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>SLA 12V 7-12Ah + charger + ATO enclosure</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="G11" s="18">
+        <f>E11*F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n"/>
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Tier 2 total</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n"/>
-      <c r="D11" s="20" t="n"/>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="11">
-        <f>SUM(G7:G10)</f>
-        <v/>
-      </c>
-      <c r="H11" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="11">
+        <f>SUM(G7:G11)</f>
+        <v/>
+      </c>
+      <c r="H12" s="20" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -1241,6 +1276,401 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Say Watt Robotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Tier 3 — Electronics, control &amp; payload</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>The brain, eyes, and hands of the ROV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Item / Part</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Part / Reference</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Unit cost</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Watertight electronics enclosure (4" tube, end caps, clamp, rails)</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Blue Robotics</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>WTE4-ASM-R1</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" s="18">
+        <f>E7*F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Penetrators &amp; waterproof connectors</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Blue Robotics</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>WetLink + Cobalt 8 + spares</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" s="18">
+        <f>E8*F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Pre-terminated tether (~25 m, neutrally buoyant)</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Blue Robotics</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Fathom Tether 8-conductor</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>600</v>
+      </c>
+      <c r="G9" s="18">
+        <f>E9*F9</f>
+        <v/>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>14 AWG silicone wire (red + black) + ring terminals + blade-fuse assortment + crimper (1.6 power-wire build)</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Amazon / McMaster</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>14AWG red+black ~6ft each, ATO fuses 3-20A</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>90</v>
+      </c>
+      <c r="G10" s="18">
+        <f>E10*F10</f>
+        <v/>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Onboard compute &amp; control (Raspberry Pi 5, Pixhawk-style FC, topside box)</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Adafruit + Blue Robotics</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>Pi 5 8GB + Navigator</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>400</v>
+      </c>
+      <c r="G11" s="18">
+        <f>E11*F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Upgraded camera &amp; vision system (low-light HD)</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>Blue Robotics</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>Low-Light HD USB Camera</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G12" s="18">
+        <f>E12*F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Depth &amp; orientation sensors (pressure + IMU)</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Blue Robotics + Adafruit</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>Bar30 + BNO055</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>170</v>
+      </c>
+      <c r="G13" s="18">
+        <f>E13*F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Pneumatic manipulator (gripper + small cylinder + tubing)</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Misc / DIY</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>Gripper + pneumatic cylinder</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>300</v>
+      </c>
+      <c r="G14" s="18">
+        <f>E14*F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="19" t="inlineStr">
+        <is>
+          <t>Funded</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="n"/>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Tier 3 total</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="20" t="n"/>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="11">
+        <f>SUM(G7:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="20" t="n"/>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1269,14 +1699,14 @@
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>Tier 3 — Electronics, control &amp; payload</t>
+          <t>Tier 4 — Tools, safety &amp; shop</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>The brain, eyes, and hands of the ROV.</t>
+          <t>Carries forward every season — buy once, use for years.</t>
         </is>
       </c>
     </row>
@@ -1337,24 +1767,24 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Watertight electronics enclosure (4" tube, end caps, clamp, rails)</t>
+          <t>Soldering stations &amp; irons (workshop set)</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Blue Robotics</t>
+          <t>Hakko / Weller via Amazon</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>WTE4-ASM-R1</t>
+          <t>FX-888D x 2</t>
         </is>
       </c>
       <c r="E7" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G7" s="18">
         <f>E7*F7</f>
@@ -1372,24 +1802,24 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>Penetrators &amp; waterproof connectors</t>
+          <t>Hand tools &amp; test equipment (multimeters, clamp meter, etc.)</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>Blue Robotics</t>
+          <t>Amazon + McMaster</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>WetLink + Cobalt 8 + spares</t>
+          <t>Fluke 117 + clamp meter kit</t>
         </is>
       </c>
       <c r="E8" s="16" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G8" s="18">
         <f>E8*F8</f>
@@ -1407,24 +1837,24 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Pre-terminated tether (~25 m, neutrally buoyant)</t>
+          <t>Safety gear (fume extractor, fire extinguisher, first-aid, mats)</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Blue Robotics</t>
+          <t>Various</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>Fathom Tether 8-conductor</t>
+          <t>Workshop safety kit</t>
         </is>
       </c>
       <c r="E9" s="16" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>600</v>
+        <v>180</v>
       </c>
       <c r="G9" s="18">
         <f>E9*F9</f>
@@ -1442,24 +1872,24 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>Onboard compute &amp; control (Raspberry Pi 5, Pixhawk-style FC, topside box)</t>
+          <t>Adhesives, sealants &amp; O-ring supplies</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Adafruit + Blue Robotics</t>
+          <t>Loctite + McMaster</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>Pi 5 8GB + Navigator</t>
+          <t>Marine epoxy + grease + O-rings</t>
         </is>
       </c>
       <c r="E10" s="16" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G10" s="18">
         <f>E10*F10</f>
@@ -1477,24 +1907,24 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Upgraded camera &amp; vision system (low-light HD)</t>
+          <t>Build consumables (wire, solder, heat-shrink, fasteners, props)</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Blue Robotics</t>
+          <t>Various</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>Low-Light HD USB Camera</t>
+          <t>Bulk pack</t>
         </is>
       </c>
       <c r="E11" s="16" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G11" s="18">
         <f>E11*F11</f>
@@ -1512,24 +1942,24 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>Depth &amp; orientation sensors (pressure + IMU)</t>
+          <t>Soldering &amp; circuit practice kits (every student)</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>Blue Robotics + Adafruit</t>
+          <t>Adafruit / Elenco</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>Bar30 + BNO055</t>
+          <t>Practice boards (qty 12)</t>
         </is>
       </c>
       <c r="E12" s="16" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="G12" s="18">
         <f>E12*F12</f>
@@ -1547,32 +1977,32 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Pneumatic manipulator (gripper + small cylinder + tubing)</t>
+          <t>SeaMATE PufferFish Practice Board Kits (per student, for 1.5)</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>Misc / DIY</t>
+          <t>SeaMATE</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>Gripper + pneumatic cylinder</t>
+          <t>PufferFish board kit × 12</t>
         </is>
       </c>
       <c r="E13" s="16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>300</v>
+        <v>15</v>
       </c>
       <c r="G13" s="18">
         <f>E13*F13</f>
         <v/>
       </c>
-      <c r="H13" s="19" t="inlineStr">
-        <is>
-          <t>Funded</t>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1580,7 +2010,7 @@
       <c r="A14" s="20" t="n"/>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Tier 3 total</t>
+          <t>Tier 4 total</t>
         </is>
       </c>
       <c r="C14" s="20" t="n"/>
@@ -1600,13 +2030,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1629,14 +2059,14 @@
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>Tier 4 — Tools, safety &amp; shop</t>
+          <t>Tier 5 — Float, documentation &amp; reliability</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Carries forward every season — buy once, use for years.</t>
+          <t>The pieces that earn points beyond the ROV — float, paper, polish.</t>
         </is>
       </c>
     </row>
@@ -1697,24 +2127,24 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Soldering stations &amp; irons (workshop set)</t>
+          <t>Vertical profiling float build (extrusion, buoyancy engine, electronics)</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Hakko / Weller via Amazon</t>
+          <t>Blue Robotics + 3D print</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>FX-888D x 2</t>
+          <t>Custom build per MATE Floats spec</t>
         </is>
       </c>
       <c r="E7" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="G7" s="18">
         <f>E7*F7</f>
@@ -1732,24 +2162,24 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>Hand tools &amp; test equipment (multimeters, clamp meter, etc.)</t>
+          <t>Float pressure sensor + battery + radio</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>Amazon + McMaster</t>
+          <t>Adafruit + Blue Robotics</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>Fluke 117 + clamp meter kit</t>
+          <t>Bar02 + 7.4V LiPo + LoRa radio</t>
         </is>
       </c>
       <c r="E8" s="16" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="G8" s="18">
         <f>E8*F8</f>
@@ -1767,24 +2197,24 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Safety gear (fume extractor, fire extinguisher, first-aid, mats)</t>
+          <t>Print + bind the technical documentation + marketing display</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Various</t>
+          <t>Local print shop</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>Workshop safety kit</t>
+          <t>Color print + binding + foam-core</t>
         </is>
       </c>
       <c r="E9" s="16" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="G9" s="18">
         <f>E9*F9</f>
@@ -1802,24 +2232,24 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>Adhesives, sealants &amp; O-ring supplies</t>
+          <t>Engineering presentation tablet + display dongle</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Loctite + McMaster</t>
+          <t>Used iPad / Amazon</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>Marine epoxy + grease + O-rings</t>
+          <t>Display kit for the judges' room</t>
         </is>
       </c>
       <c r="E10" s="16" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G10" s="18">
         <f>E10*F10</f>
@@ -1837,24 +2267,24 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Build consumables (wire, solder, heat-shrink, fasteners, props)</t>
+          <t>Capsule build kit (1.7) — PVC pipe + end caps + O-rings + marine epoxy + silicone grease + sandpaper + washcloths</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Various</t>
+          <t>Hardware store + McMaster</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>Bulk pack</t>
+          <t>4" Sch-40 PVC + caps + Buna-N O-rings + West System / JB Weld Marine</t>
         </is>
       </c>
       <c r="E11" s="16" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G11" s="18">
         <f>E11*F11</f>
@@ -1872,24 +2302,24 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>Soldering &amp; circuit practice kits (every student)</t>
+          <t>Mission props (community-pool rehearsal aids — pool rings, weighted targets)</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>Adafruit / Elenco</t>
+          <t>DIY</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>Practice boards (qty 12)</t>
+          <t>Misc props</t>
         </is>
       </c>
       <c r="E12" s="16" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G12" s="18">
         <f>E12*F12</f>
@@ -1902,346 +2332,56 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="n"/>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Tier 4 total</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="n"/>
-      <c r="D13" s="20" t="n"/>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="11">
-        <f>SUM(G7:G12)</f>
-        <v/>
-      </c>
-      <c r="H13" s="20" t="n"/>
-    </row>
-  </sheetData>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Say Watt Robotics</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>Tier 5 — Float, documentation &amp; reliability</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>The pieces that earn points beyond the ROV — float, paper, polish.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="n"/>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Item / Part</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Part / Reference</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Unit cost</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Vertical profiling float build (extrusion, buoyancy engine, electronics)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Blue Robotics + 3D print</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Custom build per MATE Floats spec</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>400</v>
-      </c>
-      <c r="G7" s="18">
-        <f>E7*F7</f>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="A13" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Photogrammetry license + storage (RealityCapture or Meshroom)</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Capturing Reality</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>Steam license per-input</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>300</v>
+      </c>
+      <c r="G13" s="18">
+        <f>E13*F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>Float pressure sensor + battery + radio</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Adafruit + Blue Robotics</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>Bar02 + 7.4V LiPo + LoRa radio</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>230</v>
-      </c>
-      <c r="G8" s="18">
-        <f>E8*F8</f>
-        <v/>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Print + bind the technical documentation + marketing display</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Local print shop</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>Color print + binding + foam-core</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="G9" s="18">
-        <f>E9*F9</f>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>Engineering presentation tablet + display dongle</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>Used iPad / Amazon</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>Display kit for the judges' room</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="G10" s="18">
-        <f>E10*F10</f>
-        <v/>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Practice ball / mission props (community-pool rehearsal aids)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>DIY</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>Misc PVC / 3D print</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>200</v>
-      </c>
-      <c r="G11" s="18">
-        <f>E11*F11</f>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Photogrammetry license + storage (RealityCapture or Meshroom)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>Capturing Reality</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>Steam license per-input</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="G12" s="18">
-        <f>E12*F12</f>
-        <v/>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="n"/>
-      <c r="B13" s="10" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="20" t="n"/>
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Tier 5 total</t>
         </is>
       </c>
-      <c r="C13" s="20" t="n"/>
-      <c r="D13" s="20" t="n"/>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="11">
-        <f>SUM(G7:G12)</f>
-        <v/>
-      </c>
-      <c r="H13" s="20" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="11">
+        <f>SUM(G7:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="20" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
